--- a/JsonConverter/ExcelFiles/AssembleTable.xlsx
+++ b/JsonConverter/ExcelFiles/AssembleTable.xlsx
@@ -19,12 +19,39 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="24">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="27">
+  <x:si>
+    <x:t>MaxUseCount</x:t>
+  </x:si>
   <x:si>
     <x:t>DisplayName</x:t>
   </x:si>
   <x:si>
     <x:t>화면 표시 이름</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MaxGauge</x:t>
+  </x:si>
+  <x:si>
+    <x:t>브레이브 어셈블</x:t>
+  </x:si>
+  <x:si>
+    <x:t>합체 지속시간(초)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Duration</x:t>
+  </x:si>
+  <x:si>
+    <x:t>최대 합체 게이지</x:t>
+  </x:si>
+  <x:si>
+    <x:t>합체 고유 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AttackSpeedMultiplier</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AttackDamageMultiplier</x:t>
   </x:si>
   <x:si>
     <x:t>서포트 프리팹 Addressables 키</x:t>
@@ -33,22 +60,34 @@
     <x:t>ID</x:t>
   </x:si>
   <x:si>
+    <x:t>스테이지당 최대 합체 횟수</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Assemble_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>공격 적중당 게이지 획득량</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GaugeGainPerHit</x:t>
+  </x:si>
+  <x:si>
     <x:t>SupportPrefabKey</x:t>
   </x:si>
   <x:si>
     <x:t>MoveSpeedMultiplier</x:t>
   </x:si>
   <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이동속도 배율</x:t>
+  </x:si>
+  <x:si>
     <x:t>float</x:t>
   </x:si>
   <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
     <x:t>stirng</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이동속도 배율</x:t>
   </x:si>
   <x:si>
     <x:t>공격력 배율</x:t>
@@ -60,37 +99,7 @@
     <x:t>Unit/Support/RhinoCarrier</x:t>
   </x:si>
   <x:si>
-    <x:t>Assemble_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>공격 적중당 게이지 획득량</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GaugeGainPerHit</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MaxGauge</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Duration</x:t>
-  </x:si>
-  <x:si>
-    <x:t>브레이브 어셈블</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AttackDamageMultiplier</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AttackSpeedMultiplier</x:t>
-  </x:si>
-  <x:si>
-    <x:t>합체 지속시간(초)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>최대 합체 게이지</x:t>
-  </x:si>
-  <x:si>
-    <x:t>합체 고유 ID</x:t>
+    <x:t>int</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -222,7 +231,7 @@
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="13">
+  <x:cellXfs count="14">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
@@ -260,6 +269,9 @@
       <x:alignment horizontal="left" vertical="bottom"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="bottom"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="left" vertical="bottom"/>
     </x:xf>
   </x:cellXfs>
@@ -875,41 +887,43 @@
     <x:col min="4" max="4" width="15.5703125" style="1" customWidth="1"/>
     <x:col min="5" max="5" width="25" style="1" customWidth="1"/>
     <x:col min="6" max="6" width="16.28515625" style="1" customWidth="1"/>
-    <x:col min="7" max="7" width="21.4296875" style="1" customWidth="1"/>
-    <x:col min="8" max="9" width="19.4296875" style="1" customWidth="1"/>
-    <x:col min="10" max="10" width="23.4296875" style="1" customWidth="1"/>
+    <x:col min="7" max="7" width="22.5703125" style="1" customWidth="1"/>
+    <x:col min="8" max="8" width="21.4296875" style="1" customWidth="1"/>
+    <x:col min="9" max="10" width="19.4296875" style="1" customWidth="1"/>
     <x:col min="11" max="16384" width="12.54296875" style="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:16384" s="6" customFormat="1" ht="15.75" customHeight="1">
       <x:c r="A1" s="7" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B1" s="7" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C1" s="7" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="D1" s="1" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="E1" s="1" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="F1" s="1" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G1" s="1" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="H1" s="1" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="B1" s="7" t="s">
-        <x:v>1</x:v>
+      <x:c r="I1" s="1" t="s">
+        <x:v>20</x:v>
       </x:c>
-      <x:c r="C1" s="7" t="s">
-        <x:v>2</x:v>
+      <x:c r="J1" s="1" t="s">
+        <x:v>24</x:v>
       </x:c>
-      <x:c r="D1" s="1" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="E1" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F1" s="1" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="G1" s="1" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="H1" s="1" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="I1" s="1" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="J1" s="1"/>
       <x:c r="K1" s="1"/>
       <x:c r="L1" s="1"/>
       <x:c r="M1" s="1"/>
@@ -17285,73 +17299,79 @@
       <x:c r="XFC1" s="1"/>
       <x:c r="XFD1" s="1"/>
     </x:row>
-    <x:row r="2" spans="1:9" ht="13.199999999999999">
+    <x:row r="2" spans="1:10" ht="13.199999999999999">
       <x:c r="A2" s="7" t="s">
-        <x:v>8</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B2" s="7" t="s">
-        <x:v>7</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C2" s="7" t="s">
-        <x:v>7</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D2" s="7" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="E2" s="7" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="F2" s="7" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="G2" s="7" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="H2" s="1" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="I2" s="1" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="J2" s="1" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" spans="1:10" s="5" customFormat="1" ht="15.75" customHeight="1">
+      <x:c r="A3" s="8" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="B3" s="8" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C3" s="8" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D3" s="5" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E3" s="5" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="F3" s="5" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="E2" s="7" t="s">
-        <x:v>6</x:v>
+      <x:c r="G3" s="5" t="s">
+        <x:v>0</x:v>
       </x:c>
-      <x:c r="F2" s="7" t="s">
-        <x:v>6</x:v>
+      <x:c r="H3" s="5" t="s">
+        <x:v>10</x:v>
       </x:c>
-      <x:c r="G2" s="1" t="s">
-        <x:v>6</x:v>
+      <x:c r="I3" s="5" t="s">
+        <x:v>18</x:v>
       </x:c>
-      <x:c r="H2" s="1" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="I2" s="1" t="s">
-        <x:v>6</x:v>
+      <x:c r="J3" s="5" t="s">
+        <x:v>9</x:v>
       </x:c>
     </x:row>
-    <x:row r="3" spans="1:9" s="5" customFormat="1" ht="15.75" customHeight="1">
-      <x:c r="A3" s="8" t="s">
-        <x:v>3</x:v>
+    <x:row r="4" spans="1:10" ht="15.75" customHeight="1">
+      <x:c r="A4" s="9" t="s">
+        <x:v>14</x:v>
       </x:c>
-      <x:c r="B3" s="8" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C3" s="8" t="s">
+      <x:c r="B4" s="9" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="D3" s="5" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="E3" s="5" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="F3" s="5" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="G3" s="5" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="H3" s="5" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="I3" s="5" t="s">
-        <x:v>20</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" spans="1:9" ht="15.75" customHeight="1">
-      <x:c r="A4" s="9" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="B4" s="9" t="s">
-        <x:v>18</x:v>
-      </x:c>
       <x:c r="C4" s="9" t="s">
-        <x:v>12</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D4" s="1">
         <x:v>100</x:v>
@@ -17362,13 +17382,16 @@
       <x:c r="F4" s="10">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="G4" s="1">
+      <x:c r="G4" s="13">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H4" s="1">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="H4" s="1">
+      <x:c r="I4" s="1">
         <x:v>1.25</x:v>
       </x:c>
-      <x:c r="I4" s="1">
+      <x:c r="J4" s="1">
         <x:v>1.5</x:v>
       </x:c>
     </x:row>
@@ -17383,9 +17406,9 @@
       <x:c r="C6" s="11"/>
     </x:row>
     <x:row r="7" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A7" s="9"/>
-      <x:c r="B7" s="9"/>
-      <x:c r="C7" s="9"/>
+      <x:c r="A7" s="11"/>
+      <x:c r="B7" s="11"/>
+      <x:c r="C7" s="11"/>
     </x:row>
     <x:row r="8" spans="1:3" ht="15.75" customHeight="1">
       <x:c r="A8" s="12"/>
@@ -17418,14 +17441,14 @@
       <x:c r="C13" s="9"/>
     </x:row>
     <x:row r="14" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A14" s="7"/>
-      <x:c r="B14" s="7"/>
-      <x:c r="C14" s="7"/>
+      <x:c r="A14" s="9"/>
+      <x:c r="B14" s="9"/>
+      <x:c r="C14" s="9"/>
     </x:row>
     <x:row r="15" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A15" s="7"/>
-      <x:c r="B15" s="7"/>
-      <x:c r="C15" s="7"/>
+      <x:c r="A15" s="9"/>
+      <x:c r="B15" s="9"/>
+      <x:c r="C15" s="9"/>
     </x:row>
     <x:row r="16" spans="1:3" ht="15.75" customHeight="1">
       <x:c r="A16" s="2"/>
